--- a/retail-audit-calc/catalog.xlsx
+++ b/retail-audit-calc/catalog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\YandexDisk\КОМДИР\ГЛАВНОЕ\корректируем и создаем файлы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1478D6-A9AC-4B3A-BFC6-C29231FCB523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB661AD-5E6B-4201-8477-725B45A1344D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9000" yWindow="0" windowWidth="14136" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4150" uniqueCount="1414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4162" uniqueCount="1417">
   <si>
     <t>Бельгийское белое</t>
   </si>
@@ -4278,6 +4278,15 @@
   </si>
   <si>
     <t>Энергетический напиток Ягуар Красный культ 0,45</t>
+  </si>
+  <si>
+    <t>Колбаски Шнеллеры с/к 85 гр. сыр Пармезан Шнеллер</t>
+  </si>
+  <si>
+    <t>Колбаски Шнеллеры с/к 85 гр. Красный перец Шнеллер</t>
+  </si>
+  <si>
+    <t>Колбаски Шнеллеры с/к 85 гр. Шнеллер</t>
   </si>
 </sst>
 </file>
@@ -4322,10 +4331,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -4606,7 +4614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1386"/>
+  <dimension ref="A1:C1390"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.77734375" customWidth="1"/>
@@ -19132,7 +19140,7 @@
       </c>
     </row>
     <row r="1323" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1323" s="2" t="s">
+      <c r="A1323" t="s">
         <v>1350</v>
       </c>
       <c r="B1323" t="s">
@@ -19143,7 +19151,7 @@
       </c>
     </row>
     <row r="1324" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1324" s="2" t="s">
+      <c r="A1324" t="s">
         <v>1351</v>
       </c>
       <c r="B1324" t="s">
@@ -19154,7 +19162,7 @@
       </c>
     </row>
     <row r="1325" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1325" s="2" t="s">
+      <c r="A1325" t="s">
         <v>1352</v>
       </c>
       <c r="B1325" t="s">
@@ -19165,7 +19173,7 @@
       </c>
     </row>
     <row r="1326" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1326" s="2" t="s">
+      <c r="A1326" t="s">
         <v>1353</v>
       </c>
       <c r="B1326" t="s">
@@ -19176,7 +19184,7 @@
       </c>
     </row>
     <row r="1327" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1327" s="2" t="s">
+      <c r="A1327" t="s">
         <v>1354</v>
       </c>
       <c r="B1327" t="s">
@@ -19187,7 +19195,7 @@
       </c>
     </row>
     <row r="1328" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1328" s="2" t="s">
+      <c r="A1328" t="s">
         <v>1355</v>
       </c>
       <c r="B1328" t="s">
@@ -19198,7 +19206,7 @@
       </c>
     </row>
     <row r="1329" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1329" s="2" t="s">
+      <c r="A1329" t="s">
         <v>1356</v>
       </c>
       <c r="B1329" t="s">
@@ -19209,7 +19217,7 @@
       </c>
     </row>
     <row r="1330" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1330" s="2" t="s">
+      <c r="A1330" t="s">
         <v>1357</v>
       </c>
       <c r="B1330" t="s">
@@ -19220,7 +19228,7 @@
       </c>
     </row>
     <row r="1331" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1331" s="2" t="s">
+      <c r="A1331" t="s">
         <v>1358</v>
       </c>
       <c r="B1331" t="s">
@@ -19231,7 +19239,7 @@
       </c>
     </row>
     <row r="1332" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1332" s="2" t="s">
+      <c r="A1332" t="s">
         <v>1359</v>
       </c>
       <c r="B1332" t="s">
@@ -19242,7 +19250,7 @@
       </c>
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1333" s="2" t="s">
+      <c r="A1333" t="s">
         <v>1360</v>
       </c>
       <c r="B1333" t="s">
@@ -19253,7 +19261,7 @@
       </c>
     </row>
     <row r="1334" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1334" s="2" t="s">
+      <c r="A1334" t="s">
         <v>1361</v>
       </c>
       <c r="B1334" t="s">
@@ -19264,7 +19272,7 @@
       </c>
     </row>
     <row r="1335" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1335" s="2" t="s">
+      <c r="A1335" t="s">
         <v>1362</v>
       </c>
       <c r="B1335" t="s">
@@ -19275,7 +19283,7 @@
       </c>
     </row>
     <row r="1336" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1336" s="2" t="s">
+      <c r="A1336" t="s">
         <v>1363</v>
       </c>
       <c r="B1336" t="s">
@@ -19286,7 +19294,7 @@
       </c>
     </row>
     <row r="1337" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1337" s="2" t="s">
+      <c r="A1337" t="s">
         <v>1364</v>
       </c>
       <c r="B1337" t="s">
@@ -19297,7 +19305,7 @@
       </c>
     </row>
     <row r="1338" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1338" s="2" t="s">
+      <c r="A1338" t="s">
         <v>1365</v>
       </c>
       <c r="B1338" t="s">
@@ -19308,7 +19316,7 @@
       </c>
     </row>
     <row r="1339" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1339" s="2" t="s">
+      <c r="A1339" t="s">
         <v>1366</v>
       </c>
       <c r="B1339" t="s">
@@ -19319,7 +19327,7 @@
       </c>
     </row>
     <row r="1340" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1340" s="2" t="s">
+      <c r="A1340" t="s">
         <v>1367</v>
       </c>
       <c r="B1340" t="s">
@@ -19330,7 +19338,7 @@
       </c>
     </row>
     <row r="1341" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1341" s="2" t="s">
+      <c r="A1341" t="s">
         <v>1368</v>
       </c>
       <c r="B1341" t="s">
@@ -19341,7 +19349,7 @@
       </c>
     </row>
     <row r="1342" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1342" s="2" t="s">
+      <c r="A1342" t="s">
         <v>1369</v>
       </c>
       <c r="B1342" t="s">
@@ -19352,7 +19360,7 @@
       </c>
     </row>
     <row r="1343" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1343" s="2" t="s">
+      <c r="A1343" t="s">
         <v>1370</v>
       </c>
       <c r="B1343" t="s">
@@ -19363,7 +19371,7 @@
       </c>
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1344" s="2" t="s">
+      <c r="A1344" t="s">
         <v>1371</v>
       </c>
       <c r="B1344" t="s">
@@ -19374,7 +19382,7 @@
       </c>
     </row>
     <row r="1345" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1345" s="2" t="s">
+      <c r="A1345" t="s">
         <v>1372</v>
       </c>
       <c r="B1345" t="s">
@@ -19385,7 +19393,7 @@
       </c>
     </row>
     <row r="1346" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1346" s="2" t="s">
+      <c r="A1346" t="s">
         <v>1373</v>
       </c>
       <c r="B1346" t="s">
@@ -19396,7 +19404,7 @@
       </c>
     </row>
     <row r="1347" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1347" s="2" t="s">
+      <c r="A1347" t="s">
         <v>1374</v>
       </c>
       <c r="B1347" t="s">
@@ -19616,7 +19624,7 @@
       </c>
     </row>
     <row r="1367" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1367" s="2" t="s">
+      <c r="A1367" t="s">
         <v>1394</v>
       </c>
       <c r="B1367" t="s">
@@ -19627,7 +19635,7 @@
       </c>
     </row>
     <row r="1368" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1368" s="2" t="s">
+      <c r="A1368" t="s">
         <v>1395</v>
       </c>
       <c r="B1368" t="s">
@@ -19638,7 +19646,7 @@
       </c>
     </row>
     <row r="1369" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1369" s="2" t="s">
+      <c r="A1369" t="s">
         <v>1396</v>
       </c>
       <c r="B1369" t="s">
@@ -19649,7 +19657,7 @@
       </c>
     </row>
     <row r="1370" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1370" s="2" t="s">
+      <c r="A1370" t="s">
         <v>1397</v>
       </c>
       <c r="B1370" t="s">
@@ -19660,7 +19668,7 @@
       </c>
     </row>
     <row r="1371" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1371" s="2" t="s">
+      <c r="A1371" t="s">
         <v>1398</v>
       </c>
       <c r="B1371" t="s">
@@ -19671,7 +19679,7 @@
       </c>
     </row>
     <row r="1372" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1372" s="2" t="s">
+      <c r="A1372" t="s">
         <v>1399</v>
       </c>
       <c r="B1372" t="s">
@@ -19682,7 +19690,7 @@
       </c>
     </row>
     <row r="1373" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1373" s="2" t="s">
+      <c r="A1373" t="s">
         <v>1400</v>
       </c>
       <c r="B1373" t="s">
@@ -19693,7 +19701,7 @@
       </c>
     </row>
     <row r="1374" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1374" s="2" t="s">
+      <c r="A1374" t="s">
         <v>1401</v>
       </c>
       <c r="B1374" t="s">
@@ -19704,7 +19712,7 @@
       </c>
     </row>
     <row r="1375" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1375" s="2" t="s">
+      <c r="A1375" t="s">
         <v>1402</v>
       </c>
       <c r="B1375" t="s">
@@ -19715,7 +19723,7 @@
       </c>
     </row>
     <row r="1376" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1376" s="2" t="s">
+      <c r="A1376" t="s">
         <v>1403</v>
       </c>
       <c r="B1376" t="s">
@@ -19726,7 +19734,7 @@
       </c>
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1377" s="2" t="s">
+      <c r="A1377" t="s">
         <v>1404</v>
       </c>
       <c r="B1377" t="s">
@@ -19737,7 +19745,7 @@
       </c>
     </row>
     <row r="1378" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1378" s="2" t="s">
+      <c r="A1378" t="s">
         <v>1405</v>
       </c>
       <c r="B1378" t="s">
@@ -19748,7 +19756,7 @@
       </c>
     </row>
     <row r="1379" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1379" s="2" t="s">
+      <c r="A1379" t="s">
         <v>1406</v>
       </c>
       <c r="B1379" t="s">
@@ -19759,7 +19767,7 @@
       </c>
     </row>
     <row r="1380" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1380" s="2" t="s">
+      <c r="A1380" t="s">
         <v>1407</v>
       </c>
       <c r="B1380" t="s">
@@ -19770,7 +19778,7 @@
       </c>
     </row>
     <row r="1381" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1381" s="2" t="s">
+      <c r="A1381" t="s">
         <v>1408</v>
       </c>
       <c r="B1381" t="s">
@@ -19781,7 +19789,7 @@
       </c>
     </row>
     <row r="1382" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1382" s="2" t="s">
+      <c r="A1382" t="s">
         <v>1409</v>
       </c>
       <c r="B1382" t="s">
@@ -19832,6 +19840,50 @@
         <v>27</v>
       </c>
       <c r="C1386" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1387" t="s">
+        <v>760</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>963</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1388" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1389" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1390" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1390" t="s">
         <v>9</v>
       </c>
     </row>

--- a/retail-audit-calc/catalog.xlsx
+++ b/retail-audit-calc/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\YandexDisk\КОМДИР\ГЛАВНОЕ\корректируем и создаем файлы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB661AD-5E6B-4201-8477-725B45A1344D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070CF0AC-2BD2-4318-B202-DC1E9F013412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4162" uniqueCount="1417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4225" uniqueCount="1438">
   <si>
     <t>Бельгийское белое</t>
   </si>
@@ -4287,6 +4287,69 @@
   </si>
   <si>
     <t>Колбаски Шнеллеры с/к 85 гр. Шнеллер</t>
+  </si>
+  <si>
+    <t>Гренки ржан-пшен Демидовские "Чеснок-Баранина"</t>
+  </si>
+  <si>
+    <t>Арахис в глазури Averton Горчица/Мёд</t>
+  </si>
+  <si>
+    <t>Жевательная резинка "Love is" Микс 4,2г</t>
+  </si>
+  <si>
+    <t>Арахис в глазури Averton Asia collection "Морской коктейль" 1кг (Авертон)</t>
+  </si>
+  <si>
+    <t>Крутоны багетные Житницкие "Вареные раки с укропом"</t>
+  </si>
+  <si>
+    <t>Миндаль (Мэджик Фуд)</t>
+  </si>
+  <si>
+    <t>Бобы солено-жареные</t>
+  </si>
+  <si>
+    <t>Арахис в глазури Averton Asia collection "Тайский перец" 1кг (Авертон)</t>
+  </si>
+  <si>
+    <t>Гренки "Нежные" "Бекон/Горчица"</t>
+  </si>
+  <si>
+    <t>Гренки ржан-пшен Демидовские "Королевский краб"</t>
+  </si>
+  <si>
+    <t>Гренки "Нежные" Розовая Паприка"</t>
+  </si>
+  <si>
+    <t>Гренки ржан-пшен Демидовские "Лук шалот"</t>
+  </si>
+  <si>
+    <t>Гренки "Нежные" "Сыр Пармезан"</t>
+  </si>
+  <si>
+    <t>Арахис Averton Хрустящая корочка "Барбекю"</t>
+  </si>
+  <si>
+    <t>Гренки ржан-пшен Демидовские "Мексиканские пряности"</t>
+  </si>
+  <si>
+    <t>Арахис Averton Хрустящая корочка "Васаби"</t>
+  </si>
+  <si>
+    <t>Гренки ржан-пшен Демидовские "Ребрышки гриль"</t>
+  </si>
+  <si>
+    <t>Кешью (Мэджик Фуд)</t>
+  </si>
+  <si>
+    <t>Арахис Averton Хрустящая корочка "Микс"</t>
+  </si>
+  <si>
+    <t>Гренки ржан-пшен Демидовские "Чеснок с копченым шпиком"</t>
+  </si>
+  <si>
+    <t>Арахис в глазури Averton Asia collection "Азиатский микс" 1кг (Авертон)</t>
   </si>
 </sst>
 </file>
@@ -4614,7 +4677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1390"/>
+  <dimension ref="A1:C1411"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.77734375" customWidth="1"/>
@@ -19887,6 +19950,237 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1391" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1391" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1392" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1393" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1394" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1395" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1396" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1397" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1398" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1399" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1400" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1401" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1402" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1403" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1404" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1405" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1406" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1407" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1408" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1409" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1410" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1411" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C1217">
     <sortCondition ref="B2:B1217"/>
